--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>3351</v>
       </c>
       <c r="Q2" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="R2" t="n">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>베라짐 하남 미사점</t>
+          <t>에이블짐 미사역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>veragym@naver.com</t>
+          <t>ablegym43@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-4012</t>
+          <t>0507-1469-2444</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
+          <t>경기 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/veragym</t>
+          <t>https://blog.naver.com/ablegym43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4095o</t>
+          <t>https://talk.naver.com/ct/w5rxl0a</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>368</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>817</v>
+        <v>1337</v>
       </c>
       <c r="R3" t="n">
-        <v>1185</v>
+        <v>2829</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1870489232</t>
+          <t>2037860861</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870489232</t>
+          <t>https://m.place.naver.com/place/2037860861</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에이블짐 미사역점</t>
+          <t>베라짐 하남 미사점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ablegym43@naver.com</t>
+          <t>veragym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1469-2444</t>
+          <t>0507-1343-4012</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
+          <t>경기 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym43</t>
+          <t>https://blog.naver.com/veragym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5rxl0a</t>
+          <t>https://talk.naver.com/ct/w4095o</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1492</v>
+        <v>368</v>
       </c>
       <c r="Q4" t="n">
-        <v>1337</v>
+        <v>818</v>
       </c>
       <c r="R4" t="n">
-        <v>2829</v>
+        <v>1186</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2037860861</t>
+          <t>1870489232</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037860861</t>
+          <t>https://m.place.naver.com/place/1870489232</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -969,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변남로 125 미사역 마이움푸르지오시티 B1</t>
+          <t>경기 하남시 미사강변남로 125 미사역 마이움푸���지오시티 B1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1016,10 +1016,10 @@
         <v>1154</v>
       </c>
       <c r="Q6" t="n">
-        <v>1311</v>
+        <v>1318</v>
       </c>
       <c r="R6" t="n">
-        <v>2465</v>
+        <v>2472</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1045,30 +1045,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에이원짐</t>
+          <t>샤인휘트니스 미사역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>aonegym8888@naver.com</t>
+          <t>shine_fitness4@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1429-6523</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
+          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aonegym8888</t>
+          <t>https://blog.naver.com/shine_fitness4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4czar</t>
+          <t>https://talk.naver.com/ct/w1sjoqj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>103</v>
+        <v>901</v>
       </c>
       <c r="Q7" t="n">
-        <v>724</v>
+        <v>2015</v>
       </c>
       <c r="R7" t="n">
-        <v>827</v>
+        <v>2916</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1771351174</t>
+          <t>1377711586</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771351174</t>
+          <t>https://m.place.naver.com/place/1377711586</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1139,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온도짐 하남시청역점</t>
+          <t>86피트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ondogym01@naver.com</t>
+          <t>86fitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-796-5025</t>
+          <t>0507-1300-6180</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 하남대로 809 2층 온도짐</t>
+          <t>경기 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ondogym01</t>
+          <t>https://cafe.naver.com/jetleezumba/28</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9c9c36</t>
+          <t>https://talk.naver.com/ct/w46038</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q8" t="n">
         <v>234</v>
       </c>
-      <c r="Q8" t="n">
-        <v>84</v>
-      </c>
       <c r="R8" t="n">
-        <v>318</v>
+        <v>665</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2009192948</t>
+          <t>1987758688</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009192948</t>
+          <t>https://m.place.naver.com/place/1987758688</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>위드짐PT 하남미사</t>
+          <t>에어바이트 PT 미사점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>withgym01@naver.com</t>
+          <t>airbite@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-8028-1929</t>
+          <t>0507-1332-4181</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변대로 84 305, 306호</t>
+          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/withgym01</t>
+          <t>https://www.instagram.com/_ko_coach</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,15 +1283,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wog61xv</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="Q9" t="n">
-        <v>334</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>447</v>
+        <v>104</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1010268294</t>
+          <t>2000579553</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010268294</t>
+          <t>https://m.place.naver.com/place/2000579553</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>한걸음 트레이닝센터 하남 미사점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>jw30-lim@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>0507-1345-9570</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://blog.naver.com/jw30-lim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1sjoqj</t>
+          <t>https://talk.naver.com/ct/w4au0e</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>901</v>
+        <v>85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2015</v>
+        <v>109</v>
       </c>
       <c r="R10" t="n">
-        <v>2916</v>
+        <v>194</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>1350773756</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/1350773756</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에어바이트 PT 미사점</t>
+          <t>하남 발란스온 필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>airbite@naver.com</t>
+          <t>balanceon7@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1332-4181</t>
+          <t>0507-1340-0381</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기 하남시 신장동로 130 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ko_coach</t>
+          <t>https://www.instagram.com/balanceon7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wog61xv</t>
+          <t>https://talk.naver.com/ct/wp15ci4</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>92</v>
+        <v>223</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>449</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>672</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,113 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2000579553</t>
+          <t>1660993198</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000579553</t>
+          <t>https://m.place.naver.com/place/1660993198</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>jw30-lim@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1345-9570</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/jw30-lim</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4au0e</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>109</v>
-      </c>
-      <c r="R12" t="n">
-        <v>194</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1350773756</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,30 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐맥스 미사역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymax_01@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>070-5250-1905</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
+          <t>경기도 하남시 상산곡동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymax_01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wr0uh6r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3351</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1328828814</t>
+          <t>1909111158</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328828814</t>
+          <t>https://m.place.naver.com/place/1909111158</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에이블짐 미사역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ablegym43@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1469-2444</t>
+          <t>070-4535-7191</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
+          <t>경기도 하남시 배알미동</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegym43</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5rxl0a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1492</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1337</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2829</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2037860861</t>
+          <t>1357580966</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037860861</t>
+          <t>https://m.place.naver.com/place/1357580966</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>베라짐 하남 미사점</t>
+          <t>신장여성헬스클럽</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>veragym@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1343-4012</t>
+          <t>031-793-3337</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
+          <t>경기도 하남시 신장로 127-1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/veragym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,24 +784,20 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4095o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>368</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>818</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1186</v>
+        <v>7</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1870489232</t>
+          <t>19077254</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870489232</t>
+          <t>https://m.place.naver.com/place/19077254</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,39 +846,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>워터캐슬 하남미사점</t>
+          <t>여성전용 헬스 그룹PT 핏걸 미사점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>watercastle-misa@naver.com</t>
+          <t>fitgirl24@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>031-792-1118</t>
+          <t>0507-1355-3459</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 하남시 미사대로 410 오벨리스크 지하1층</t>
+          <t>경기도 하남시 미사강변동로84번길 39 7층 여성전용 핏걸 미사역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://watercastle-misa.kr</t>
+          <t>https://blog.naver.com/fitgirl24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,17 +888,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vabi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1305</v>
+        <v>354</v>
       </c>
       <c r="Q5" t="n">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="R5" t="n">
-        <v>1682</v>
+        <v>827</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1929061645</t>
+          <t>1322437220</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1929061645</t>
+          <t>https://m.place.naver.com/place/1322437220</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -947,44 +935,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>카인드짐24시 헬스 PT 미사역점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kindgym8@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1459-2444</t>
+          <t>070-8934-7264</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변남로 125 미사역 마이움푸���지오시티 B1</t>
+          <t>경기도 하남시 덕풍동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_zxeEXK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -994,32 +982,28 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4m5k0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1154</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1318</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2472</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1845162608</t>
+          <t>1424575675</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845162608</t>
+          <t>https://m.place.naver.com/place/1424575675</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1045,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>프리짐24 하남시청점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>freegym24hanam@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>0507-1304-3912</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기도 하남시 대청로 30 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://www.instagram.com/freegym24h</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1sjoqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>901</v>
+        <v>36</v>
       </c>
       <c r="Q7" t="n">
-        <v>2015</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>2916</v>
+        <v>48</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>1244046567</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/1244046567</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1123,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>86피트니스</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86fitness@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1300-6180</t>
+          <t>070-5250-5038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
+          <t>경기도 하남시 상사창동</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/jetleezumba/28</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,24 +1160,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46038</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1987758688</t>
+          <t>1989120909</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987758688</t>
+          <t>https://m.place.naver.com/place/1989120909</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에어바이트 PT 미사점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>airbite@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1332-4181</t>
+          <t>070-5250-5946</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기도 하남시 초일동</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ko_coach</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1288,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wog61xv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2000579553</t>
+          <t>1846877235</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000579553</t>
+          <t>https://m.place.naver.com/place/1846877235</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jw30-lim@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1345-9570</t>
+          <t>070-4536-3243</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+          <t>경기도 하남시 초일동</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jw30-lim</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,24 +1348,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4au0e</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1350773756</t>
+          <t>1124458136</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
+          <t>https://m.place.naver.com/place/1124458136</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하남 발란스온 필라테스</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>balanceon7@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1340-0381</t>
+          <t>070-5250-4973</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 하남시 신장동로 130 4층</t>
+          <t>경기도 하남시 항동</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/balanceon7</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1442,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1484,14 +1452,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wp15ci4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,15 +1482,7863 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1660993198</t>
+          <t>1591888892</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1660993198</t>
+          <t>https://m.place.naver.com/place/1591888892</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>070-5250-9598</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 하남시 항동</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1673352967</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1673352967</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>아지트32 미사점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1442-0438</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로84번길 39 10층 키네틱캠프</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kinetic_camp?igsh=eGxhb2gxbWd2bmh1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>89</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1060993266</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1060993266</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070-5250-8785</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하사창동</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1844382434</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1844382434</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SM헬스</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>srysky@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로 130-5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>19278274</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19278274</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>포시즌휘트니스&amp;골프 하남미사점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fseason792@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1380-1636</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 73 노블레스타워 11층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fseason792</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>760</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1204</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1964</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>624955172</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/624955172</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>짐큐어</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gymcure@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1385-1589</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례대로 190 상가 2층 205,206호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymcure_wirye</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R17" t="n">
+        <v>74</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1606342077</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606342077</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>유나이티드 앤드업 스포츠 재활센터</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sook8014@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1318-0941</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 48 해든마루유나이티드 4층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unitedandup_official</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>33</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1268621730</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1268621730</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>070-4561-5538</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장동</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1407839354</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1407839354</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>메가나인 피트니스 하남미사역점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>meganine1771@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1427-3418</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 95 힐스테이트미사역 그랑파사쥬 2층 2005호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meganine_misa</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1848</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3348</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1443046036</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443046036</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>070-8934-2815</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감이동</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1419256481</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1419256481</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>크로스핏 발리인미사 하남 미사역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>crossfit_bali@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1358-8955</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 180 힐스테이트 미사역 그랑파사쥬 3층 3001-1호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_bali</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>517</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>236</v>
+      </c>
+      <c r="R22" t="n">
+        <v>753</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1486337625</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1486337625</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>에이치스튜디오 멀티짐</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>enchant0907@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로170번길 10</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1695228823</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1695228823</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>에이원짐</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>aonegym8888@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/aonegym8888</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>724</v>
+      </c>
+      <c r="R24" t="n">
+        <v>827</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1771351174</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1771351174</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>려</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4leaf5719@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>031-795-3002</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로 150 준 빌딩 6층 려액션휘트니스</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>36</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>20336603</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20336603</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>짐자반 헬스PT 하남시청역점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>yongchun8447@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1309-7009</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 851 지하1층 짐자반 헬스PT 하남시청역점</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymjaban_hanam?igsh=aDd6bXhldWtyZ2Ru</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2058715985</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2058715985</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>워터캐슬 하남미사점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>watercastle-misa@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>031-792-1118</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 410 오벨리스크 지하1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://watercastle-misa.kr</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1305</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>377</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1682</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1929061645</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1929061645</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>문스타휘트니스 미사점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>moonstarfitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1307-3454</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로204번길 45 성산타워플러스 10층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moonstarfitness3</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>552</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>817</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1369</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1808080383</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1808080383</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>번짐 PT STUDIO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>misaburngym@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1353-5258</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 190 상가 303~305호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/misaburngym</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>70</v>
+      </c>
+      <c r="R29" t="n">
+        <v>135</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1679144863</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1679144863</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>점핑하이 감이점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일백제로180번길 17 818, 819호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1807923971</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1807923971</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>에스필라피티 부영상가점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>pilatespt2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1486-9209</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로 119-1 3층 305호, 306호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2011604523</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2011604523</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>하남파워리프팅</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 270-1 미사강변호반써밋 1층 1-107호, 1-108호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hanam_powerlifting</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>16</v>
+      </c>
+      <c r="R32" t="n">
+        <v>294</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1861206341</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1861206341</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>시티짐 하남점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>citygymhanam@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1397-8319</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로 33 11층 시티짐 하남점</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/citygymhanam</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>573</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>850</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1423</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1754842803</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1754842803</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>여성전용 헬스 PT 레이디짐 미사점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fitgirl24@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1345-3449</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로84번길 39 7층 레이디짐 미사점</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitgirl24</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>498</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>615</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1113</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1945229916</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945229916</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>올데이휘트니스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>alldayfitness_tennis@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1301-8101</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일백제로 175 3층 올데이휘트니스</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://alldayfitness.co.kr/</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1491</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>177</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1668</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1444576791</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1444576791</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>070-4556-4505</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 하남시 상산곡동</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1275422077</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1275422077</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>트렌드짐 헬스&amp;PT 하남검단산역점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>trendgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1333-5495</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장동로 162 지하1층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/trendgym-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>26</v>
+      </c>
+      <c r="R37" t="n">
+        <v>145</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2086490541</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2086490541</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>세탁소</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>세탁업체헬스장세탁유니폼세탁수건세탁업체,세탁공장</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>total_clean_laundry@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>070-8069-2057</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일동</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1777133835</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1777133835</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>해머짐 하남미사점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hammergym0122@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1484-8823</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 70 해오름프라자 7층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hammergym0122</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>540</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>625</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1165</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1443515030</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443515030</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>문스타휘트니스&amp;골프 황산점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>moonstarfitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>031-5175-7345</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변서로 16 하우스디스마트밸리 SB 190호 문스타휘트니스</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moonstarfitness4</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>163</v>
+      </c>
+      <c r="R40" t="n">
+        <v>486</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1397882457</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397882457</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>에스필라피티 하남검단산역점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pilatespt2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1439-9208</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장동로 162 2층 에스필라피티 하남검단산역점</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilatespt2021</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>157</v>
+      </c>
+      <c r="R41" t="n">
+        <v>219</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1291927376</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1291927376</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AMG피트니스 감일점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>amg_hanam@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1410-0151</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일백제로 161 6층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/amg_hanam</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>3169</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>239</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3408</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1677076802</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1677076802</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>시티짐하남점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>031-795-0099</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로 33</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1271258567</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1271258567</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>070-5250-2741</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 하남시 풍산동</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1498029641</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1498029641</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>스카이짐X스카이필라테스 미사점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>skygym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1366-5752</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 135 나동 2층 246호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skygym_misa</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>608</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1453</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2061</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1138019549</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1138019549</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>피트니스에이치PT 하남시청점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>fitnessh3@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1462-2103</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로 26 1001호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessh3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1447</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>228</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1675</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1149308441</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149308441</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>뚝딱짐</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ttukttakgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1418-8489</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 82 서건미사메트로타워 4층 401호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_yKvyxj</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>48</v>
+      </c>
+      <c r="R47" t="n">
+        <v>89</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1967276250</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1967276250</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>엑시트짐 헬스&amp;PT 감일점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>exitgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1369-9646</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신우실로63번길 15 4층 엑시트짐</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/exitgym</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>594</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>255</v>
+      </c>
+      <c r="R48" t="n">
+        <v>849</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1951430318</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951430318</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>카인드짐24시 헬스 PT 미사역점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>kindgym8@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1459-2444</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 125 미사역 마이움푸르지오시티 B1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_zxeEXK</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1154</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1318</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2472</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1845162608</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845162608</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>070-4542-1629</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 하남시 상사창동</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1432411766</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1432411766</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>커브스 미사강변클럽</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>j_mikiwi3434@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>031-792-7330</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 10층 1005호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/j_mikiwi3434</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>88</v>
+      </c>
+      <c r="R51" t="n">
+        <v>115</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>752050920</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/752050920</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>070-4535-1347</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감이동</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1498792527</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1498792527</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>크로스핏 스네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>cfsnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1352-4631</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 하남시 세미로 33 도윤빌딩B 지하1층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_snail</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>104</v>
+      </c>
+      <c r="R53" t="n">
+        <v>276</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1808755113</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1808755113</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>인피니트짐</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>kissn1234@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1344-9750</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로226번안길 9 미사드림타워 2층 204호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_Tbghn</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4jcle</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>28</v>
+      </c>
+      <c r="R54" t="n">
+        <v>43</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1078203476</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1078203476</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>온도짐 하남시청역점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ondogym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>031-796-5025</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 809 2층 온도짐</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ondogym01</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>234</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>84</v>
+      </c>
+      <c r="R55" t="n">
+        <v>318</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2009192948</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2009192948</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>070-4536-1717</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 하남시 선동</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1589439970</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1589439970</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>바른브랜딩 마케팅</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>logixwin12@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1344-5613</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로 9 7층 709호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/logixwin12</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>72</v>
+      </c>
+      <c r="R57" t="n">
+        <v>72</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2096966726</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2096966726</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>에어바이트 PT 미사점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>airbite@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1332-4181</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 279 3층 311, 312호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_ko_coach</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>12</v>
+      </c>
+      <c r="R58" t="n">
+        <v>104</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2000579553</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2000579553</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>아이엠피티</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>iampt0411@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1422-0411</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로170번길 10 401호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/iampt0411</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>367</v>
+      </c>
+      <c r="R59" t="n">
+        <v>454</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1817320671</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817320671</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>귤녀홈짐</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>angelicbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1339-6783</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 72 4층 401~2호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/gyulgym/profile</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>14</v>
+      </c>
+      <c r="R60" t="n">
+        <v>147</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1161866508</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161866508</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SUN PT STUDIO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로204번길 22 3층 312호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>5</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1789251026</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1789251026</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PT라잍</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>lright_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1369-2544</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례학암로14번길 35 207호(경서타워1)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lright_pt</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>89</v>
+      </c>
+      <c r="R62" t="n">
+        <v>231</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1814212750</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814212750</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>더블엠PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sjwlgns@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1425-4478</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로364번길 32 드림프라자 2층 더블엠PT스튜디오</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sjwlgns</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>47</v>
+      </c>
+      <c r="R63" t="n">
+        <v>77</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1129855753</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129855753</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>운동재활연구소</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>fc_kickers@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1374-3294</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신우실로 83 3층 스포츠재활 센터</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kickers.sports_at</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>12</v>
+      </c>
+      <c r="R64" t="n">
+        <v>12</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1681478954</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1681478954</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>에이스 피티</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1acept@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1452-2242</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 90 202호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/acept_hanam</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>102</v>
+      </c>
+      <c r="R65" t="n">
+        <v>252</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1479304301</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479304301</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>김성현PT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ksh_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1317-2667</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일중앙로 60 벨솔레파크 307호 김성현PT</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ksh_pt</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>16</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2046362916</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046362916</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>그로우걸 여성전용 그룹PT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>growgirl_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1343-0367</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신평로 49 6층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/growgirl_fit</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>80</v>
+      </c>
+      <c r="R67" t="n">
+        <v>87</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2003214630</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2003214630</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>퍼스트PT 하남미사점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>volleystar1@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1395-0293</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 520 현대지식산업센터한강미사2차 25블럭 C동 2층 214호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>5</v>
+      </c>
+      <c r="R68" t="n">
+        <v>10</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1614642225</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614642225</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>레이크짐 PT 미사점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>lakegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1469-4114</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lakegym</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>500</v>
+      </c>
+      <c r="R69" t="n">
+        <v>787</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1857191169</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1857191169</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>더하남 그룹PT 키네틱캠프 미사점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>mvppvm@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1387-4464</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mvppvm/222632646985</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>753</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>328</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1081</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1949849359</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1949849359</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>미사PT 코치짐</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>coachgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>031-794-3041</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 127 경서타워 809호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_CxexcwG/chat</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>462</v>
+      </c>
+      <c r="R71" t="n">
+        <v>542</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1595778485</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1595778485</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>루트핏PT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>rf_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1359-0739</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 38 2층 204호, 204-1호 루트핏</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rootfit_pt/</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>6</v>
+      </c>
+      <c r="R72" t="n">
+        <v>56</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1904278776</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1904278776</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>세븐렙스 PT Studio</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>spxkzjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1411-0033</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일중앙로 60 5층 509호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/7reps_pt_studio</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>4</v>
+      </c>
+      <c r="R73" t="n">
+        <v>14</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1285774796</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285774796</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>샤인휘트니스 미사역점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>shine_fitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1429-6523</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/shine_fitness4</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2015</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2916</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1377711586</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1377711586</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>엠씨 피티 하남미사점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mcptkoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1317-4657</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로334번안길 11 101호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mcptkoo</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>95</v>
+      </c>
+      <c r="R75" t="n">
+        <v>182</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1140998386</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140998386</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>두바이짐 PT</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kmc4400@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1366-0994</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로34번길 82 골드프라자 4층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kmc4400</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>241</v>
+      </c>
+      <c r="R76" t="n">
+        <v>244</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1219615517</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219615517</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>블루바디</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>blue_body@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1488-1000</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 125 미사 푸르지오시티 A동 상가 319호</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@pafacoach</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>79</v>
+      </c>
+      <c r="R77" t="n">
+        <v>100</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1938079941</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1938079941</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>원스피티</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1329-8769</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>경기도 하남시 세미로1길 5 힐즈파크프라자 203호 원스피티</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ones_pt__</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5</v>
+      </c>
+      <c r="R78" t="n">
+        <v>10</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1018969451</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1018969451</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>한걸음 트레이닝센터 하남 미사점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jw30-lim@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1345-9570</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jw30-lim</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>109</v>
+      </c>
+      <c r="R79" t="n">
+        <v>194</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1350773756</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1350773756</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>트레스비짐 PT</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>kungfu85@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1316-3618</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로54번길 75 3층 313호</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kungfu85</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>34</v>
+      </c>
+      <c r="R80" t="n">
+        <v>40</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1359685947</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359685947</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>워크아웃짐 하남미사점</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1330-2337</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 1201호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/workoutgym_2017</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>67</v>
+      </c>
+      <c r="R81" t="n">
+        <v>230</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1137767219</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137767219</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 미사역</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ghpt38@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1305-1428</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 270-1 미사강변 호반 써밋 201동 2층 2-180호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://vo.la/GC9p1L6</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>240</v>
+      </c>
+      <c r="R82" t="n">
+        <v>561</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1965066669</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1965066669</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 미사 2호</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>goodhabitmisa2@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1386-1531</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로204번길 21 미사엘큐브 2층 좋은습관</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodhabitpt_misa2</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>137</v>
+      </c>
+      <c r="R83" t="n">
+        <v>485</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1646172726</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646172726</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>나우PT스튜디오 하남 미사점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>10007shp@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1340-6252</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 3층 303호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/now_pt_studio</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>510</v>
+      </c>
+      <c r="R84" t="n">
+        <v>786</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1514647381</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1514647381</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>위드짐 그라운드</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pums60@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1326-9200</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 45 골든브릿지상가 207호</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://instagram.com/today_gym_misa</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>32</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1355241607</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355241607</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>다짐피티전문샵</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>da-gym-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1428-9887</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로802번길 11 국보빌딩 2층 다짐</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/da-gym-pt</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>19</v>
+      </c>
+      <c r="R86" t="n">
+        <v>66</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>36542396</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36542396</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>바른피티</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ibelongtoj@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1316-7191</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로 156 하남프라자 205호 바른피티</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barun__pt</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>10</v>
+      </c>
+      <c r="R87" t="n">
+        <v>76</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1774046248</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1774046248</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>황인성 PT STUDIO 하남시청점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>insung9188@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1401-9188</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 788 3층 황인성 PT STUDIO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@ptstudio3687</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>241</v>
+      </c>
+      <c r="R88" t="n">
+        <v>390</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1460727979</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1460727979</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>본짐</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>borngym_00@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1418-3837</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로226번길 15 예스프라자포틴 4층 401호</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/borngym_kmsj</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>47</v>
+      </c>
+      <c r="R89" t="n">
+        <v>61</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>302988601</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/302988601</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>워크아웃짐 랜드마인유니버시티</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ordinaryworkout@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1471-5515</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 1202호</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://workoutgym.co.kr/</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>355</v>
+      </c>
+      <c r="R90" t="n">
+        <v>750</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1531145636</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1531145636</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>포데이짐PT 하남미사점</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>fourdaygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1347-3173</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 81 5층 502호</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fourdaygym</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>447</v>
+      </c>
+      <c r="R91" t="n">
+        <v>686</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1167442751</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1167442751</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>카인드인베스트먼트</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>yanggundesign@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1355-7383</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 125 102동 2층 214,215호</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yanggundesign</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>9</v>
+      </c>
+      <c r="R92" t="n">
+        <v>9</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1368931279</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1368931279</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>너와 온 디자인 오피스</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>designpress2016@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1498-5126</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 550 10층 제씨 10-0001호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neowaon</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>3</v>
+      </c>
+      <c r="R93" t="n">
+        <v>3</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1699692256</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699692256</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>탁구장</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>조탁구 아카데미</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>jo_pingpong@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1428-3081</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로226번안길 21 파인빌딩 4층 조탁구 아카데미</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@pingpong_JO</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>8</v>
+      </c>
+      <c r="R94" t="n">
+        <v>50</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1077462514</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077462514</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>베델필라테스앤요가</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>bethelpilayoga_@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1311-6523</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로34번안길 11 3층</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bethelpilates?igsh=MTU4czE5YW1sMTliYQ==</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>4</v>
+      </c>
+      <c r="R95" t="n">
+        <v>55</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>2045003601</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045003601</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -5689,34 +5689,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>광고대행</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>바른브랜딩 마케팅</t>
+          <t>블리스 우먼 피트니스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>logixwin12@naver.com</t>
+          <t>turinj9@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1344-5613</t>
+          <t>0507-1385-3452</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 하남시 대청로 9 7층 709호</t>
+          <t>경기도 하남시 미사강변중앙로 220 1104호~1106호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/logixwin12</t>
+          <t>https://www.instagram.com/bliss_fitness_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5747,17 +5747,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="Q57" t="n">
-        <v>72</v>
+        <v>751</v>
       </c>
       <c r="R57" t="n">
-        <v>72</v>
+        <v>881</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,12 +5766,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2096966726</t>
+          <t>1594837551</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096966726</t>
+          <t>https://m.place.naver.com/place/1594837551</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5783,34 +5783,34 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에어바이트 PT 미사점</t>
+          <t>아인스휘트니스 헬스 PT 골프 GX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>airbite@naver.com</t>
+          <t>einsfitness@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1332-4181</t>
+          <t>0507-1344-8363</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기도 하남시 신장로 151 대동피렌체 지하1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ko_coach</t>
+          <t>https://www.instagram.com/e1nsfitness?igsh=M3R5dnU5MWYxamR0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>92</v>
+        <v>573</v>
       </c>
       <c r="Q58" t="n">
-        <v>12</v>
+        <v>864</v>
       </c>
       <c r="R58" t="n">
-        <v>104</v>
+        <v>1437</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2000579553</t>
+          <t>468234581</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000579553</t>
+          <t>https://m.place.naver.com/place/468234581</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5877,34 +5877,34 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아이엠피티</t>
+          <t>올타임짐 PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>iampt0411@naver.com</t>
+          <t>alltimegym_@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1422-0411</t>
+          <t>0507-1310-2811</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로170번길 10 401호</t>
+          <t>경기도 하남시 하남대로 843 신정프라자 2층 203호 올타임짐</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iampt0411</t>
+          <t>https://www.instagram.com/alltimegym_goat/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5930,7 +5930,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5939,13 +5939,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="Q59" t="n">
-        <v>367</v>
+        <v>10</v>
       </c>
       <c r="R59" t="n">
-        <v>454</v>
+        <v>22</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1817320671</t>
+          <t>2075217648</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817320671</t>
+          <t>https://m.place.naver.com/place/2075217648</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5971,49 +5971,49 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>귤녀홈짐</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>angelicbody@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1339-6783</t>
+          <t>070-5250-9492</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로 72 4층 401~2호</t>
+          <t>경기도 하남시 선동</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/gyulgym/profile</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6029,17 +6029,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1161866508</t>
+          <t>1661272859</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161866508</t>
+          <t>https://m.place.naver.com/place/1661272859</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6065,17 +6065,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SUN PT STUDIO</t>
+          <t>짐맥스 미사역점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>gymax_01@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -6083,12 +6083,12 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로204번길 22 3층 312호</t>
+          <t>경기도 하남시 미사강변동로84번길 21 남송타워 9층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gymax_01</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6119,17 +6119,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3352</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>654</v>
       </c>
       <c r="R61" t="n">
-        <v>5</v>
+        <v>4006</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,12 +6138,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1789251026</t>
+          <t>1328828814</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1789251026</t>
+          <t>https://m.place.naver.com/place/1328828814</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6155,34 +6155,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PT라잍</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>lright_pt@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1369-2544</t>
+          <t>070-4561-1484</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 하남시 위례학암로14번길 35 207호(경서타워1)</t>
+          <t>경기도 하남시 감일동</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lright_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6213,17 +6213,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,12 +6232,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1814212750</t>
+          <t>1965720237</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814212750</t>
+          <t>https://m.place.naver.com/place/1965720237</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6249,34 +6249,34 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>더블엠PT스튜디오</t>
+          <t>크로스핏 미사</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sjwlgns@naver.com</t>
+          <t>crossfitmisa@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1425-4478</t>
+          <t>0507-1351-1399</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변한강로364번길 32 드림프라자 2층 더블엠PT스튜디오</t>
+          <t>경기도 하남시 미사강변동로 95 미사역 그랑파사쥬 2층 2049호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sjwlgns</t>
+          <t>https://www.instagram.com/crossfit_misa</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6311,13 +6311,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>30</v>
+        <v>281</v>
       </c>
       <c r="Q63" t="n">
-        <v>47</v>
+        <v>505</v>
       </c>
       <c r="R63" t="n">
-        <v>77</v>
+        <v>786</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1129855753</t>
+          <t>1306570326</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1129855753</t>
+          <t>https://m.place.naver.com/place/1306570326</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6343,34 +6343,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>운동재활연구소</t>
+          <t>밀론부티크 본점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>fc_kickers@naver.com</t>
+          <t>milonkoreaofficial@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1374-3294</t>
+          <t>0507-1390-9883</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 하남시 신우실로 83 3층 스포츠재활 센터</t>
+          <t>경기도 하남시 미사대로 410 미사강변오벨리스크 312호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kickers.sports_at</t>
+          <t>https://www.instagram.com/milonboutique_official/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6405,13 +6405,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>182</v>
       </c>
       <c r="R64" t="n">
-        <v>12</v>
+        <v>305</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1681478954</t>
+          <t>1044239447</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1681478954</t>
+          <t>https://m.place.naver.com/place/1044239447</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6437,34 +6437,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에이스 피티</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1acept@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1452-2242</t>
+          <t>070-8934-5365</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로 90 202호</t>
+          <t>경기도 하남시 배알미동</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/acept_hanam</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6495,17 +6495,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1479304301</t>
+          <t>1053754646</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1479304301</t>
+          <t>https://m.place.naver.com/place/1053754646</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6531,34 +6531,34 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>김성현PT</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ksh_pt@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1317-2667</t>
+          <t>070-8934-5010</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 하남시 감일중앙로 60 벨솔레파크 307호 김성현PT</t>
+          <t>경기도 하남시 광암동</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ksh_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6593,13 +6593,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,12 +6608,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2046362916</t>
+          <t>1276515413</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2046362916</t>
+          <t>https://m.place.naver.com/place/1276515413</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6625,34 +6625,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>그로우걸 여성전용 그룹PT</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>growgirl_fit@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1343-0367</t>
+          <t>070-5250-3392</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 하남시 신평로 49 6층</t>
+          <t>경기도 하남시 신장동</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/growgirl_fit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2003214630</t>
+          <t>1802845758</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2003214630</t>
+          <t>https://m.place.naver.com/place/1802845758</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6719,34 +6719,38 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>퍼스트PT 하남미사점</t>
+          <t>F45 미사</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>volleystar1@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>turinj9@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>misa@f45training.kr</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1395-0293</t>
+          <t>0507-1366-3812</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사대로 520 현대지식산업센터한강미사2차 25블럭 C동 2층 214호</t>
+          <t>경기도 하남시 미사강변중앙로204번길 22 207호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://f45training.kr/misa</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6777,17 +6781,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>433</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>271</v>
       </c>
       <c r="R68" t="n">
-        <v>10</v>
+        <v>704</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6796,12 +6800,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1614642225</t>
+          <t>1652668857</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614642225</t>
+          <t>https://m.place.naver.com/place/1652668857</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6813,34 +6817,34 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>레이크짐 PT 미사점</t>
+          <t>스포애니 하남시청역점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lakegym@naver.com</t>
+          <t>spoany466@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1469-4114</t>
+          <t>0507-1415-6681</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
+          <t>경기도 하남시 신평로 84 동화건설 주차빌딩 2층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lakegym</t>
+          <t>https://blog.naver.com/spoany466</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6855,7 +6859,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6866,7 +6870,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6875,13 +6879,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>287</v>
+        <v>1382</v>
       </c>
       <c r="Q69" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="R69" t="n">
-        <v>787</v>
+        <v>2382</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6890,12 +6894,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1857191169</t>
+          <t>132730406</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857191169</t>
+          <t>https://m.place.naver.com/place/132730406</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6907,34 +6911,34 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>더하남 그룹PT 키네틱캠프 미사점</t>
+          <t>커브스 신장클럽</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>mvppvm@naver.com</t>
+          <t>holthanam_2030@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1387-4464</t>
+          <t>031-796-8090</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+          <t>경기도 하남시 대청로 29 대유빌딩 5층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mvppvm/222632646985</t>
+          <t>http://www.curveskorea.co.kr/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6960,22 +6964,22 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>753</v>
+        <v>190</v>
       </c>
       <c r="Q70" t="n">
-        <v>328</v>
+        <v>32</v>
       </c>
       <c r="R70" t="n">
-        <v>1081</v>
+        <v>222</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6984,12 +6988,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1949849359</t>
+          <t>13534745</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949849359</t>
+          <t>https://m.place.naver.com/place/13534745</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7001,44 +7005,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>카달로그인쇄</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>미사PT 코치짐</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>coachgym@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>031-794-3041</t>
+          <t>070-4546-2699</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로 127 경서타워 809호</t>
+          <t>경기도 하남시 하사창동</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_CxexcwG/chat</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7054,22 +7058,22 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>542</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7078,12 +7082,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1595778485</t>
+          <t>1302824585</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1595778485</t>
+          <t>https://m.place.naver.com/place/1302824585</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7095,34 +7099,34 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>루트핏PT</t>
+          <t>스카이피트니스x골프x복싱</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>rf_pt@naver.com</t>
+          <t>skygym2@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1359-0739</t>
+          <t>0507-1340-8354</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로 38 2층 204호, 204-1호 루트핏</t>
+          <t>경기도 하남시 미사대로 540 현대지식산업센터한강미사2차 A ,B동 B1층 002호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rootfit_pt/</t>
+          <t>https://blog.naver.com/skygym2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7137,7 +7141,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7148,7 +7152,7 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7157,13 +7161,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>1403</v>
       </c>
       <c r="R72" t="n">
-        <v>56</v>
+        <v>1685</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7172,12 +7176,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1904278776</t>
+          <t>1024532712</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1904278776</t>
+          <t>https://m.place.naver.com/place/1024532712</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7189,34 +7193,34 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>세븐렙스 PT Studio</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>spxkzjs12@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1411-0033</t>
+          <t>070-4535-8008</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 하남시 감일중앙로 60 5층 509호</t>
+          <t>경기도 하남시 항동</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/7reps_pt_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7226,7 +7230,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7247,17 +7251,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7266,12 +7270,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1285774796</t>
+          <t>1217799665</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285774796</t>
+          <t>https://m.place.naver.com/place/1217799665</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7283,34 +7287,34 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>201피트니스 헬스 PT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>jwjwjw1004@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>0507-1423-0157</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기도 하남시 덕풍동로 111-15 리치플러스 하남센터 6층 604호 ~ 606호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://blog.naver.com/jwjwjw1004</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7341,17 +7345,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>901</v>
+        <v>31</v>
       </c>
       <c r="Q74" t="n">
-        <v>2015</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>2916</v>
+        <v>36</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7360,12 +7364,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>1763868615</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/1763868615</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7377,34 +7381,34 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>엠씨 피티 하남미사점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mcptkoo@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1317-4657</t>
+          <t>070-5250-1307</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변한강로334번안길 11 101호</t>
+          <t>경기도 하남시 춘궁동</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mcptkoo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7414,12 +7418,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7439,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7454,12 +7458,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1140998386</t>
+          <t>1082456654</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140998386</t>
+          <t>https://m.place.naver.com/place/1082456654</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7471,34 +7475,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>두바이짐 PT</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kmc4400@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1366-0994</t>
+          <t>070-4556-0939</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로34번길 82 골드프라자 4층</t>
+          <t>경기도 하남시 춘궁동</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kmc4400</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7508,12 +7512,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7529,17 +7533,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,12 +7552,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1219615517</t>
+          <t>1069894729</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219615517</t>
+          <t>https://m.place.naver.com/place/1069894729</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -7565,34 +7569,34 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>블루바디</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>blue_body@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1488-1000</t>
+          <t>070-8934-6434</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로 125 미사 푸르지오시티 A동 상가 319호</t>
+          <t>경기도 하남시 감일동</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://youtube.com/@pafacoach</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7602,7 +7606,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7627,13 +7631,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7642,12 +7646,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1938079941</t>
+          <t>1211482364</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1938079941</t>
+          <t>https://m.place.naver.com/place/1211482364</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -7659,30 +7663,34 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>원스피티</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>그로우짐 PT&amp;헬스 하남시청점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>thehanam_grow24@naver.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1329-8769</t>
+          <t>070-4149-0366</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>경기도 하남시 세미로1길 5 힐즈파크프라자 203호 원스피티</t>
+          <t>경기도 하남시 신평로 49 B1층</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ones_pt__</t>
+          <t>https://blog.naver.com/thehanam_grow24</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7697,7 +7705,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -7717,13 +7725,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>5</v>
+        <v>276</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>323</v>
       </c>
       <c r="R78" t="n">
-        <v>10</v>
+        <v>599</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7732,12 +7740,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1018969451</t>
+          <t>1151553186</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018969451</t>
+          <t>https://m.place.naver.com/place/1151553186</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -7749,34 +7757,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
+          <t>올라와 피트니스 PT 미사점</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jw30-lim@naver.com</t>
+          <t>allawafitness1@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1345-9570</t>
+          <t>0507-1421-8108</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+          <t>경기도 하남시 미사강변대로 62 바토프라자 7층 올라와피트니스</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jw30-lim</t>
+          <t>https://www.instagram.com/allawa_fit</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7791,7 +7799,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7811,13 +7819,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Q79" t="n">
-        <v>109</v>
+        <v>480</v>
       </c>
       <c r="R79" t="n">
-        <v>194</v>
+        <v>972</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7826,12 +7834,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1350773756</t>
+          <t>1270980317</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
+          <t>https://m.place.naver.com/place/1270980317</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -7843,39 +7851,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>트레스비짐 PT</t>
+          <t>라곰트레이닝 미사</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>kungfu85@naver.com</t>
+          <t>uisangka@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1316-3618</t>
+          <t>0507-1372-8340</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로54번길 75 3층 313호</t>
+          <t>경기도 하남시 미사강변중앙로 193 에코브릿지 3층 301호</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kungfu85</t>
+          <t>https://www.lagomtraining.co.kr/misa</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7885,7 +7893,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7905,13 +7913,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="Q80" t="n">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="R80" t="n">
-        <v>40</v>
+        <v>353</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7920,12 +7928,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1359685947</t>
+          <t>1808366166</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1359685947</t>
+          <t>https://m.place.naver.com/place/1808366166</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -7937,34 +7945,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>워크아웃짐 하남미사점</t>
+          <t>에이블짐 미사역점</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>ablegym43@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1330-2337</t>
+          <t>0507-1469-2444</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 1201호</t>
+          <t>경기도 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/workoutgym_2017</t>
+          <t>https://blog.naver.com/ablegym43</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7979,7 +7987,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -7999,13 +8007,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>163</v>
+        <v>1494</v>
       </c>
       <c r="Q81" t="n">
-        <v>67</v>
+        <v>1337</v>
       </c>
       <c r="R81" t="n">
-        <v>230</v>
+        <v>2831</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8014,12 +8022,12 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1137767219</t>
+          <t>2037860861</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137767219</t>
+          <t>https://m.place.naver.com/place/2037860861</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8031,44 +8039,44 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 미사역</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ghpt38@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1305-1428</t>
+          <t>070-4536-2822</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변한강로 270-1 미사강변 호반 써밋 201동 2층 2-180호</t>
+          <t>경기도 하남시 풍산동</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://vo.la/GC9p1L6</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8089,17 +8097,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>561</v>
+        <v>0</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8108,12 +8116,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1965066669</t>
+          <t>1314174543</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965066669</t>
+          <t>https://m.place.naver.com/place/1314174543</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8125,34 +8133,34 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 미사 2호</t>
+          <t>타고사이클 하남점</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>goodhabitmisa2@naver.com</t>
+          <t>tagocycle1@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1386-1531</t>
+          <t>0507-1338-8382</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로204번길 21 미사엘큐브 2층 좋은습관</t>
+          <t>경기도 하남시 미사강변동로 79 미사역타워 1306호</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodhabitpt_misa2</t>
+          <t>https://blog.naver.com/tagocycle1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8167,7 +8175,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8187,13 +8195,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>348</v>
+        <v>975</v>
       </c>
       <c r="Q83" t="n">
-        <v>137</v>
+        <v>470</v>
       </c>
       <c r="R83" t="n">
-        <v>485</v>
+        <v>1445</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8202,12 +8210,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1646172726</t>
+          <t>1850143871</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1646172726</t>
+          <t>https://m.place.naver.com/place/1850143871</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8219,34 +8227,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>나우PT스튜디오 하남 미사점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10007shp@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1340-6252</t>
+          <t>070-4561-8946</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 3층 303호</t>
+          <t>경기도 하남시 광암동</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/now_pt_studio</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8256,7 +8264,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8277,17 +8285,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8296,12 +8304,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1514647381</t>
+          <t>1628899128</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1514647381</t>
+          <t>https://m.place.naver.com/place/1628899128</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -8313,34 +8321,34 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>위드짐 그라운드</t>
+          <t>타임짐휘트니스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>pums60@naver.com</t>
+          <t>timesportsss@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1326-9200</t>
+          <t>0507-1469-3171</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변남로 45 골든브릿지상가 207호</t>
+          <t>경기도 하남시 더우개로 29 6층, 7층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://instagram.com/today_gym_misa</t>
+          <t>https://blog.naver.com/timesportsss</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8355,7 +8363,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8371,17 +8379,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="R85" t="n">
-        <v>32</v>
+        <v>301</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8390,12 +8398,12 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1355241607</t>
+          <t>1246104749</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1355241607</t>
+          <t>https://m.place.naver.com/place/1246104749</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -8407,34 +8415,34 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>다짐피티전문샵</t>
+          <t>케이스포츠</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>da-gym-pt@naver.com</t>
+          <t>dm_eng@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1428-9887</t>
+          <t>0507-1356-3363</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>경기도 하남시 하남대로802번길 11 국보빌딩 2층 다짐</t>
+          <t>경기도 하남시 미사강변한강로 60-4 uz센터 지하1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/da-gym-pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8444,12 +8452,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8465,17 +8473,17 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8484,12 +8492,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>36542396</t>
+          <t>1109405743</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36542396</t>
+          <t>https://m.place.naver.com/place/1109405743</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -8501,34 +8509,34 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>바른피티</t>
+          <t>베라짐 하남 미사점</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ibelongtoj@naver.com</t>
+          <t>veragym@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1316-7191</t>
+          <t>0507-1343-4012</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>경기도 하남시 신장로 156 하남프라자 205호 바른피티</t>
+          <t>경기도 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barun__pt</t>
+          <t>https://blog.naver.com/veragym</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8543,7 +8551,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8563,13 +8571,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>66</v>
+        <v>368</v>
       </c>
       <c r="Q87" t="n">
-        <v>10</v>
+        <v>819</v>
       </c>
       <c r="R87" t="n">
-        <v>76</v>
+        <v>1187</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8578,12 +8586,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1774046248</t>
+          <t>1870489232</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774046248</t>
+          <t>https://m.place.naver.com/place/1870489232</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -8595,39 +8603,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>황인성 PT STUDIO 하남시청점</t>
+          <t>에그짐 미사역점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>insung9188@naver.com</t>
+          <t>eggym-misa@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0507-1401-9188</t>
+          <t>0507-1416-9050</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>경기도 하남시 하남대로 788 3층 황인성 PT STUDIO</t>
+          <t>경기도 하남시 미사강변중앙로204번길 22 3층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://youtube.com/@ptstudio3687</t>
+          <t>http://www.eggym.co.kr</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8637,7 +8645,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8648,7 +8656,7 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -8657,13 +8665,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>149</v>
+        <v>399</v>
       </c>
       <c r="Q88" t="n">
-        <v>241</v>
+        <v>1172</v>
       </c>
       <c r="R88" t="n">
-        <v>390</v>
+        <v>1571</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8672,12 +8680,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1460727979</t>
+          <t>1244434346</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1460727979</t>
+          <t>https://m.place.naver.com/place/1244434346</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -8689,34 +8697,34 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>본짐</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>borngym_00@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0507-1418-3837</t>
+          <t>070-4536-4447</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로226번길 15 예스프라자포틴 4층 401호</t>
+          <t>경기도 하남시 덕풍동</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/borngym_kmsj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8726,7 +8734,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8747,17 +8755,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8766,12 +8774,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>302988601</t>
+          <t>1707593187</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/302988601</t>
+          <t>https://m.place.naver.com/place/1707593187</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8788,34 +8796,34 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>워크아웃짐 랜드마인유니버시티</t>
+          <t>디짐 헬스 PT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ordinaryworkout@naver.com</t>
+          <t>d_gym2025@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1471-5515</t>
+          <t>0507-1495-1161</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 1202호</t>
+          <t>경기도 하남시 미사강변대로226번안길 25 401~402호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://workoutgym.co.kr/</t>
+          <t>https://blog.naver.com/d_gym2025</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8825,7 +8833,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -8841,17 +8849,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>395</v>
+        <v>10</v>
       </c>
       <c r="Q90" t="n">
-        <v>355</v>
+        <v>120</v>
       </c>
       <c r="R90" t="n">
-        <v>750</v>
+        <v>130</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8860,12 +8868,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1531145636</t>
+          <t>1856686041</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531145636</t>
+          <t>https://m.place.naver.com/place/1856686041</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -8877,34 +8885,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>포데이짐PT 하남미사점</t>
+          <t>바른브랜딩 마케팅</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>fourdaygym@naver.com</t>
+          <t>logixwin12@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1347-3173</t>
+          <t>0507-1344-5613</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변동로 81 5층 502호</t>
+          <t>경기도 하남시 대청로 9 7층 709호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fourdaygym</t>
+          <t>https://blog.naver.com/logixwin12</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8935,17 +8943,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>447</v>
+        <v>72</v>
       </c>
       <c r="R91" t="n">
-        <v>686</v>
+        <v>72</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8954,12 +8962,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1167442751</t>
+          <t>2096966726</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167442751</t>
+          <t>https://m.place.naver.com/place/2096966726</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -8971,34 +8979,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>세탁</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>카인드인베스트먼트</t>
+          <t>홍크린</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>yanggundesign@naver.com</t>
+          <t>greenhouse7784@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1355-7383</t>
+          <t>0507-1404-9874</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변남로 125 102동 2층 214,215호</t>
+          <t>경기도 하남시 하남대로654번길 24-43</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yanggundesign</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9008,12 +9016,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9029,17 +9037,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q92" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9048,12 +9056,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1368931279</t>
+          <t>38404070</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1368931279</t>
+          <t>https://m.place.naver.com/place/38404070</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9065,34 +9073,34 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>너와 온 디자인 오피스</t>
+          <t>에어바이트 PT 미사점</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>designpress2016@naver.com</t>
+          <t>airbite@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1498-5126</t>
+          <t>0507-1332-4181</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사대로 550 10층 제씨 10-0001호</t>
+          <t>경기도 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/neowaon</t>
+          <t>https://www.instagram.com/_ko_coach</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9127,13 +9135,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="Q93" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9142,12 +9150,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1699692256</t>
+          <t>2000579553</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699692256</t>
+          <t>https://m.place.naver.com/place/2000579553</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -9159,34 +9167,34 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>탁구장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>조탁구 아카데미</t>
+          <t>아이엠피티</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jo_pingpong@naver.com</t>
+          <t>iampt0411@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1428-3081</t>
+          <t>0507-1422-0411</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로226번안길 21 파인빌딩 4층 조탁구 아카데미</t>
+          <t>경기도 하남시 미사강변중앙로170번길 10 401호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://youtube.com/@pingpong_JO</t>
+          <t>https://blog.naver.com/iampt0411</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9201,7 +9209,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9212,7 +9220,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9221,13 +9229,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="Q94" t="n">
-        <v>8</v>
+        <v>367</v>
       </c>
       <c r="R94" t="n">
-        <v>50</v>
+        <v>454</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9236,12 +9244,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1077462514</t>
+          <t>1817320671</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077462514</t>
+          <t>https://m.place.naver.com/place/1817320671</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -9253,39 +9261,39 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>베델필라테스앤요가</t>
+          <t>귤녀홈짐</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>bethelpilayoga_@naver.com</t>
+          <t>angelicbody@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0507-1311-6523</t>
+          <t>0507-1339-6783</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>경기도 하남시 미사강변대로34번안길 11 3층</t>
+          <t>경기도 하남시 미사강변동로 72 4층 401~2호</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bethelpilates?igsh=MTU4czE5YW1sMTliYQ==</t>
+          <t>https://smartstore.naver.com/gyulgym/profile</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9295,7 +9303,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9315,30 +9323,5642 @@
         </is>
       </c>
       <c r="P95" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>14</v>
+      </c>
+      <c r="R95" t="n">
+        <v>147</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1161866508</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1161866508</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SUN PT STUDIO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로204번길 22 3층 312호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>5</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1789251026</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1789251026</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PT라잍</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>lright_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1369-2544</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례학암로14번길 35 207호(경서타워1)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lright_pt</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>89</v>
+      </c>
+      <c r="R97" t="n">
+        <v>231</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1814212750</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814212750</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>더블엠PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>sjwlgns@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1425-4478</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로364번길 32 드림프라자 2층 더블엠PT스튜디오</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sjwlgns</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>47</v>
+      </c>
+      <c r="R98" t="n">
+        <v>77</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1129855753</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1129855753</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>운동재활연구소</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>fc_kickers@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1374-3294</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신우실로 83 3층 스포츠재활 센터</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kickers.sports_at</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>12</v>
+      </c>
+      <c r="R99" t="n">
+        <v>12</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1681478954</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1681478954</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>에이스 피티</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1acept@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1452-2242</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 90 202호</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/acept_hanam</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>102</v>
+      </c>
+      <c r="R100" t="n">
+        <v>252</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1479304301</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479304301</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>김성현PT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ksh_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0507-1317-2667</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일중앙로 60 벨솔레파크 307호 김성현PT</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ksh_pt</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>16</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>2046362916</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2046362916</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>그로우걸 여성전용 그룹PT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>growgirl_fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1343-0367</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신평로 49 6층</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/growgirl_fit</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>80</v>
+      </c>
+      <c r="R102" t="n">
+        <v>87</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>2003214630</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2003214630</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>퍼스트PT 하남미사점</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>volleystar1@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1395-0293</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 520 현대지식산업센터한강미사2차 25블럭 C동 2층 214호</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>5</v>
+      </c>
+      <c r="R103" t="n">
+        <v>10</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1614642225</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614642225</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>레이크짐 PT 미사점</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>lakegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0507-1469-4114</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 208 13층 레이크짐</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lakegym</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>500</v>
+      </c>
+      <c r="R104" t="n">
+        <v>787</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>1857191169</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1857191169</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>더하남 그룹PT 키네틱캠프 미사점</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>mvppvm@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0507-1387-4464</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로84번길 39 에코타워 10층 1008호 키네틱캠프 미사역점</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mvppvm/222632646985</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>753</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>328</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1081</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1949849359</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1949849359</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>미사PT 코치짐</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>coachgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>031-794-3041</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 127 경서타워 809호</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_CxexcwG/chat</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>462</v>
+      </c>
+      <c r="R106" t="n">
+        <v>542</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>1595778485</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1595778485</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>루트핏PT</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>rf_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0507-1359-0739</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 38 2층 204호, 204-1호 루트핏</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rootfit_pt/</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>6</v>
+      </c>
+      <c r="R107" t="n">
+        <v>56</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>1904278776</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1904278776</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>세븐렙스 PT Studio</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>spxkzjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0507-1411-0033</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일중앙로 60 5층 509호</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/7reps_pt_studio</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>4</v>
+      </c>
+      <c r="R108" t="n">
+        <v>14</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>1285774796</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285774796</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>샤인휘트니스 미사역점</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>shine_fitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0507-1429-6523</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/shine_fitness4</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>2015</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2916</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>1377711586</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1377711586</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>엠씨 피티 하남미사점</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>mcptkoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0507-1317-4657</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로334번안길 11 101호</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mcptkoo</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>95</v>
+      </c>
+      <c r="R110" t="n">
+        <v>182</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>1140998386</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140998386</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>두바이짐 PT</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>kmc4400@naver.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0507-1366-0994</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로34번길 82 골드프라자 4층</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kmc4400</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>241</v>
+      </c>
+      <c r="R111" t="n">
+        <v>244</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>1219615517</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1219615517</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>블루바디</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>blue_body@naver.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1488-1000</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 125 미사 푸르지오시티 A동 상가 319호</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@pafacoach</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>79</v>
+      </c>
+      <c r="R112" t="n">
+        <v>100</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>1938079941</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1938079941</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>원스피티</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1329-8769</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>경기도 하남시 세미로1길 5 힐즈파크프라자 203호 원스피티</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ones_pt__</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>5</v>
+      </c>
+      <c r="R113" t="n">
+        <v>10</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>1018969451</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1018969451</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>한걸음 트레이닝센터 하남 미사점</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jw30-lim@naver.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0507-1345-9570</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jw30-lim</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>109</v>
+      </c>
+      <c r="R114" t="n">
+        <v>194</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>1350773756</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1350773756</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>트레스비짐 PT</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>kungfu85@naver.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0507-1316-3618</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로54번길 75 3층 313호</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kungfu85</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>34</v>
+      </c>
+      <c r="R115" t="n">
+        <v>40</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>1359685947</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359685947</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>워크아웃짐 하남미사점</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>j1024up@naver.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0507-1330-2337</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 1201호</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/workoutgym_2017</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>67</v>
+      </c>
+      <c r="R116" t="n">
+        <v>230</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>1137767219</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1137767219</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 미사역</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ghpt38@naver.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0507-1305-1428</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 270-1 미사강변 호반 써밋 201동 2층 2-180호</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://vo.la/GC9p1L6</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>240</v>
+      </c>
+      <c r="R117" t="n">
+        <v>561</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>1965066669</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1965066669</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 미사 2호</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>goodhabitmisa2@naver.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0507-1386-1531</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로204번길 21 미사엘큐브 2층 좋은습관</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodhabitpt_misa2</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>137</v>
+      </c>
+      <c r="R118" t="n">
+        <v>485</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>1646172726</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646172726</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>나우PT스튜디오 하남 미사점</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>10007shp@naver.com</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0507-1340-6252</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 3층 303호</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/now_pt_studio</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>510</v>
+      </c>
+      <c r="R119" t="n">
+        <v>786</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>1514647381</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1514647381</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>위드짐 그라운드</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>pums60@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0507-1326-9200</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 45 골든브릿지상가 207호</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://instagram.com/today_gym_misa</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>32</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>1355241607</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355241607</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>다짐피티전문샵</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>da-gym-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0507-1428-9887</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로802번길 11 국보빌딩 2층 다짐</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/da-gym-pt</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>19</v>
+      </c>
+      <c r="R121" t="n">
+        <v>66</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>36542396</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36542396</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>바른피티</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ibelongtoj@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0507-1316-7191</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로 156 하남프라자 205호 바른피티</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barun__pt</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>10</v>
+      </c>
+      <c r="R122" t="n">
+        <v>76</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>1774046248</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1774046248</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>황인성 PT STUDIO 하남시청점</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>insung9188@naver.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0507-1401-9188</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 788 3층 황인성 PT STUDIO</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@ptstudio3687</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>241</v>
+      </c>
+      <c r="R123" t="n">
+        <v>390</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>1460727979</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1460727979</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>본짐</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>borngym_00@naver.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0507-1418-3837</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로226번길 15 예스프라자포틴 4층 401호</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/borngym_kmsj</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>47</v>
+      </c>
+      <c r="R124" t="n">
+        <v>61</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>302988601</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/302988601</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>워크아웃짐 랜드마인유니버시티</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ordinaryworkout@naver.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0507-1471-5515</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 220 우성미사타워 1202호</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://workoutgym.co.kr/</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>355</v>
+      </c>
+      <c r="R125" t="n">
+        <v>750</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>1531145636</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1531145636</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>포데이짐PT 하남미사점</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>fourdaygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0507-1347-3173</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변동로 81 5층 502호</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fourdaygym</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>239</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>447</v>
+      </c>
+      <c r="R126" t="n">
+        <v>686</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>1167442751</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1167442751</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>라라pt</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>dae497@naver.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>0507-1493-4888</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로 130-5 8층</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dae497</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>11</v>
+      </c>
+      <c r="R127" t="n">
+        <v>18</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>1266846915</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1266846915</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>포유짐</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>4u_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0507-1337-0623</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로 270-1 미사강변호반써밋 2층 161,162호 포유짐</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/4u_gym</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>106</v>
+      </c>
+      <c r="R128" t="n">
+        <v>192</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>1919851464</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1919851464</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>여성전용 그룹PT 엑서트 위례점</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>exert_701@naver.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0507-1388-2755</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례학암로14번길 31 경서타워2 7층</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_JQgan</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>251</v>
+      </c>
+      <c r="R129" t="n">
+        <v>276</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2027288661</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2027288661</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>장우성GYM</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>wkdqudgh8765@naver.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0507-1336-0820</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>경기도 하남시 대청로59번길 24 동일상가 301호</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s6xPc4Hh</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>532</v>
+      </c>
+      <c r="R130" t="n">
+        <v>600</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>1451669930</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1451669930</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>뉴짐스PT&amp;크루</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>woongchan_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0507-1342-3414</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 214 미사역레이크더타워 6층</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/woongchan_pt</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>615</v>
+      </c>
+      <c r="R131" t="n">
+        <v>756</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>1577544321</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577544321</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>마스터피스짐 덕풍점</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>masterpiecegym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>031-791-7880</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>경기도 하남시 하남대로 843 신정프라자 2층 203호 마스터피스짐</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/masterpiecegym2</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>184</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>683</v>
+      </c>
+      <c r="R132" t="n">
+        <v>867</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>1036950683</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036950683</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>챌린지 피티샵</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>seokgi9909@naver.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0507-1345-4667</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장동로 35</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seokgi9909</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>159</v>
+      </c>
+      <c r="R133" t="n">
+        <v>261</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>1954165803</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1954165803</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>kork. 재활트레이닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>kork_training_studi0@naver.com</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0507-1361-4193</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 38 7층 kork. 트레이닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kork_training_studi0</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>15</v>
+      </c>
+      <c r="R134" t="n">
+        <v>30</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>1221331712</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1221331712</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>저스트펀크루 스튜디오</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 540 현대지식산업센터한강미사2차 B동 719호</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>1174225447</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174225447</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>삐짐</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>b_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0507-1372-3461</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>경기도 하남시 덕풍북로 2 2층</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/b__gym</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>42</v>
+      </c>
+      <c r="R136" t="n">
+        <v>108</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>1048885336</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1048885336</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>셀린1:1PT스튜디오 북위례 본점</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>seline_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0507-1464-2557</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례학암로 23 1층</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seline_pt</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>52</v>
+      </c>
+      <c r="R137" t="n">
+        <v>142</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>1559021358</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1559021358</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>웰컴피트니스 풍산점</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>welcomefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0507-1485-7234</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>경기도 하남시 덕풍동로 111 9층</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/welcome__fit</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>69</v>
+      </c>
+      <c r="R138" t="n">
+        <v>176</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>2076027825</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2076027825</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>굿데이짐 하남미사점</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>gooddaygym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0507-1412-1206</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변서로 25 미사테스타 타워 1층 R118, R119호</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gooddaygym1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>485</v>
+      </c>
+      <c r="R139" t="n">
+        <v>610</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>1282965769</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282965769</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>유케이서비스</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ukservice1@naver.com</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>031-794-6691</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변서로 16 하우스디스마트밸리 F613</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ukservice1</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>3</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>1675630387</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1675630387</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>아벨짐PT 하남미사점</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>romangfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0507-1432-1803</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 87 스타파크 2층 203호, 212호</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/romangfit_</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>153</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>658</v>
+      </c>
+      <c r="R141" t="n">
+        <v>811</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1383123287</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1383123287</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>프롬더스트릿 하남미사점</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>fromthestreet@naver.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0507-1369-1637</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변중앙로 189 307호</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Fromthestreet</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>371</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>108</v>
+      </c>
+      <c r="R142" t="n">
+        <v>479</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>1280710452</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280710452</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>위드짐PT 하남미사</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>withgym01@naver.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>031-8028-1929</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로 84 305, 306호</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/withgym01</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>334</v>
+      </c>
+      <c r="R143" t="n">
+        <v>447</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>1010268294</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1010268294</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>오늘의GYM</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ht-minrak@naver.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0507-1376-4313</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변한강로136번안길 4 1층 오늘의GYM</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/today__gym_misa</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>5</v>
+      </c>
+      <c r="R144" t="n">
+        <v>19</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>1187324622</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1187324622</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>더숨체형교정PT센터 하남미사점</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2sy_lab@naver.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 410 상가동 4층 418호 더숨 체형교정PT센터</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/2sy_lab</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>36</v>
+      </c>
+      <c r="R145" t="n">
+        <v>62</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>1077350202</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077350202</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>아마레PT</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>amarepilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0507-1353-8997</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 87 201호</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amare_pt_pilates</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>16</v>
+      </c>
+      <c r="R146" t="n">
+        <v>19</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2047714177</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2047714177</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>허니비 트레이닝</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>young_cute_@naver.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 410 . 상가동 342. 343. 344. 416호</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/honey.b_tr?igsh=djNta21sb3V0MGI4</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>10</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2050833431</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2050833431</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>바벨 미사점</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>barbell01@naver.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0507-1339-6658</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변북로30번길 34 1층</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barbell01</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>24</v>
+      </c>
+      <c r="R148" t="n">
+        <v>63</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>1431797248</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1431797248</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>86피트니스</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>86fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0507-1300-6180</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>경기도 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/jetleezumba/28</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>431</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>234</v>
+      </c>
+      <c r="R149" t="n">
+        <v>665</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1987758688</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1987758688</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>카인드인베스트먼트</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>yanggundesign@naver.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1355-7383</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변남로 125 102동 2층 214,215호</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yanggundesign</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>9</v>
+      </c>
+      <c r="R150" t="n">
+        <v>9</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>1368931279</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1368931279</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>너와 온 디자인 오피스</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>designpress2016@naver.com</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0507-1498-5126</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사대로 550 10층 제씨 10-0001호</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neowaon</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>3</v>
+      </c>
+      <c r="R151" t="n">
+        <v>3</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>1699692256</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699692256</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>탁구장</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>조탁구 아카데미</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jo_pingpong@naver.com</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0507-1428-3081</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로226번안길 21 파인빌딩 4층 조탁구 아카데미</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@pingpong_JO</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>8</v>
+      </c>
+      <c r="R152" t="n">
+        <v>50</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>1077462514</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077462514</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>베델필라테스앤요가</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>bethelpilayoga_@naver.com</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0507-1311-6523</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>경기도 하남시 미사강변대로34번안길 11 3층</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bethelpilates?igsh=MTU4czE5YW1sMTliYQ==</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
         <v>51</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="Q153" t="n">
         <v>4</v>
       </c>
-      <c r="R95" t="n">
+      <c r="R153" t="n">
         <v>55</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T95" t="inlineStr">
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
         <is>
           <t>2045003601</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="U153" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2045003601</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>라라필라테스 PT 하남덕풍점</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>rara8587@naver.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0507-1425-2211</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>경기도 하남시 신장로 130-5 8층</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rara8587</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>219</v>
+      </c>
+      <c r="R154" t="n">
+        <v>331</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>1416789753</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1416789753</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>더베러필라테스 감일점</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>better2599@naver.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>경기도 하남시 감일백제로180번길 20 반도 유스퀘어 6층 608호, 609호</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/better2599</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>211</v>
+      </c>
+      <c r="R155" t="n">
+        <v>297</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>1694041382</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1694041382</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,24 +564,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 미사역점</t>
+          <t>짐맥스 미사역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegym43@naver.com</t>
+          <t>gymax_01@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1469-2444</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
+          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5rxl0a</t>
+          <t>https://talk.naver.com/ct/wr0uh6r</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>3362</v>
       </c>
       <c r="Q2" t="n">
-        <v>1337</v>
+        <v>654</v>
       </c>
       <c r="R2" t="n">
-        <v>2833</v>
+        <v>4016</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2037860861</t>
+          <t>1328828814</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037860861</t>
+          <t>https://m.place.naver.com/place/1328828814</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐맥스 미사역점</t>
+          <t>에이블짐 미사역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gymax_01@naver.com</t>
+          <t>ablegym43@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1469-2444</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
+          <t>경기 하남시 미사강변동로 127 경서타워 10층 1001호-1012호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymax_01</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0uh6r</t>
+          <t>https://talk.naver.com/ct/w5rxl0a</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3362</v>
+        <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>654</v>
+        <v>1337</v>
       </c>
       <c r="R3" t="n">
-        <v>4016</v>
+        <v>2833</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1328828814</t>
+          <t>2037860861</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328828814</t>
+          <t>https://m.place.naver.com/place/2037860861</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -918,10 +918,10 @@
         <v>1155</v>
       </c>
       <c r="Q5" t="n">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="R5" t="n">
-        <v>2473</v>
+        <v>2477</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,36 +940,36 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>위드짐PT 하남미사</t>
+          <t>온도짐 하남시청역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>withgym01@naver.com</t>
+          <t>ondogym01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>031-8028-1929</t>
+          <t>031-796-5025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변대로 84 305, 306호</t>
+          <t>경기 하남시 하남대로 809 2층 온도짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,13 +994,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9c9c36</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="Q6" t="n">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="R6" t="n">
-        <v>447</v>
+        <v>318</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1010268294</t>
+          <t>2009192948</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010268294</t>
+          <t>https://m.place.naver.com/place/2009192948</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1046,24 +1050,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>위드짐PT 하남미사</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jbc5034@naver.com</t>
+          <t>withgym01@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>031-8028-1929</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기 하남시 미사강변대로 84 305, 306호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1088,14 +1092,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w1sjoqj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>901</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="n">
-        <v>2015</v>
+        <v>334</v>
       </c>
       <c r="R7" t="n">
-        <v>2916</v>
+        <v>447</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>1010268294</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/1010268294</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1144,24 +1144,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>86피트니스</t>
+          <t>샤인휘트니스 미사역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>86fitness@naver.com</t>
+          <t>jbc5034@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1300-6180</t>
+          <t>0507-1429-6523</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 위례학암로 18 가하프라자 4층 401, 402호</t>
+          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46038</t>
+          <t>https://talk.naver.com/ct/w1sjoqj</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>431</v>
+        <v>901</v>
       </c>
       <c r="Q8" t="n">
-        <v>234</v>
+        <v>2015</v>
       </c>
       <c r="R8" t="n">
-        <v>665</v>
+        <v>2916</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1987758688</t>
+          <t>1377711586</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1987758688</t>
+          <t>https://m.place.naver.com/place/1377711586</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1426,36 +1426,36 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하남 발란스온 필라테스</t>
+          <t>프롬더스트릿 하남미사점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>balanceon7@naver.com</t>
+          <t>fromthestreet@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1340-0381</t>
+          <t>0507-1369-1637</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 하남시 신장동로 130 4층</t>
+          <t>경기 하남시 미사강변중앙로 189 307호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wp15ci4</t>
+          <t>https://talk.naver.com/ct/w4g1gj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>223</v>
+        <v>371</v>
       </c>
       <c r="Q11" t="n">
-        <v>449</v>
+        <v>108</v>
       </c>
       <c r="R11" t="n">
-        <v>672</v>
+        <v>479</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1660993198</t>
+          <t>1280710452</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1660993198</t>
+          <t>https://m.place.naver.com/place/1280710452</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐맥스 미사역점</t>
+          <t>베라짐 하남 미사점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gymax_01@naver.com</t>
+          <t>veragym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1343-4012</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
+          <t>경기 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/veragym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wr0uh6r</t>
+          <t>https://talk.naver.com/ct/w4095o</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3371</v>
+        <v>368</v>
       </c>
       <c r="Q2" t="n">
-        <v>660</v>
+        <v>820</v>
       </c>
       <c r="R2" t="n">
-        <v>4031</v>
+        <v>1188</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1328828814</t>
+          <t>1870489232</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328828814</t>
+          <t>https://m.place.naver.com/place/1870489232</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>베라짐 하남 미사점</t>
+          <t>워터캐슬 하남미사점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>veragym@naver.com</t>
+          <t>watercastle-misa@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-4012</t>
+          <t>031-792-1118</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변대로226번길 9 송하빌딩 7층 베라짐</t>
+          <t>경기 하남시 미사대로 410 오벨리스크 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://watercastle-misa.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4095o</t>
+          <t>https://talk.naver.com/ct/w5vabi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>368</v>
+        <v>1307</v>
       </c>
       <c r="Q3" t="n">
-        <v>819</v>
+        <v>377</v>
       </c>
       <c r="R3" t="n">
-        <v>1187</v>
+        <v>1684</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1870489232</t>
+          <t>1929061645</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870489232</t>
+          <t>https://m.place.naver.com/place/1929061645</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,39 +760,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>워터캐슬 하남미사점</t>
+          <t>짐맥스 미사역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>watercastle-misa@naver.com</t>
+          <t>gymax_01@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>031-792-1118</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 하남시 미사대로 410 오벨리스크 지하1층</t>
+          <t>경기 하남시 미사강변동로84번길 21 남송타워 9층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://watercastle-misa.kr</t>
+          <t>https://blog.naver.com/gymax_01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vabi</t>
+          <t>https://talk.naver.com/ct/wr0uh6r</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1307</v>
+        <v>3375</v>
       </c>
       <c r="Q4" t="n">
-        <v>377</v>
+        <v>666</v>
       </c>
       <c r="R4" t="n">
-        <v>1684</v>
+        <v>4041</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1929061645</t>
+          <t>1328828814</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1929061645</t>
+          <t>https://m.place.naver.com/place/1328828814</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="Q5" t="n">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="R5" t="n">
-        <v>2845</v>
+        <v>2850</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="Q6" t="n">
         <v>177</v>
       </c>
       <c r="R6" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1050,29 +1050,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온도짐 하남시청역점</t>
+          <t>에이원짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ondogym01@naver.com</t>
+          <t>aonegym8888@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>031-796-5025</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 하남대로 809 2층 온도짐</t>
+          <t>경기 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/aonegym8888</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1078,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9c9c36</t>
+          <t>https://talk.naver.com/ct/w4czar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="Q7" t="n">
-        <v>84</v>
+        <v>730</v>
       </c>
       <c r="R7" t="n">
-        <v>319</v>
+        <v>833</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2009192948</t>
+          <t>1771351174</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009192948</t>
+          <t>https://m.place.naver.com/place/1771351174</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>포시즌휘트니스&amp;골프 하남미사점</t>
+          <t>온도짐 하남시청역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fseason792@naver.com</t>
+          <t>ondogym01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1380-1636</t>
+          <t>031-796-5025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변동로 73 노블레스타워 11층</t>
+          <t>경기 하남시 하남대로 809 2층 온도짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ondogym01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,12 +1176,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1195,12 +1191,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4915n</t>
+          <t>https://talk.naver.com/ct/w9c9c36</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>766</v>
+        <v>235</v>
       </c>
       <c r="Q8" t="n">
-        <v>1217</v>
+        <v>84</v>
       </c>
       <c r="R8" t="n">
-        <v>1983</v>
+        <v>319</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>624955172</t>
+          <t>2009192948</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/624955172</t>
+          <t>https://m.place.naver.com/place/2009192948</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1268,7 +1264,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/withgym01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,12 +1274,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1345,7 +1341,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jbc5034@naver.com</t>
+          <t>shine_fitness4@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1362,7 +1358,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/shine_fitness4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1368,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="Q10" t="n">
         <v>2016</v>
       </c>
       <c r="R10" t="n">
-        <v>2925</v>
+        <v>2927</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_ko_coach</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,7 +1466,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1536,29 +1532,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
+          <t>셀린1:1PT스튜디오 북위례 본점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jw30-lim@naver.com</t>
+          <t>seline_pt@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1345-9570</t>
+          <t>0507-1464-2557</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+          <t>경기 하남시 위례학암로 23 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/seline_pt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,12 +1564,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1583,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4au0e</t>
+          <t>https://talk.naver.com/ct/w45s2o</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="n">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="R12" t="n">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1608,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1350773756</t>
+          <t>1559021358</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
+          <t>https://m.place.naver.com/place/1559021358</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1629,34 +1625,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>셀린1:1PT스튜디오 북위례 본점</t>
+          <t>하남 발란스온 필라테스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>seline_pt@naver.com</t>
+          <t>balanceon7@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1464-2557</t>
+          <t>0507-1340-0381</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 하남시 위례학암로 23 1층</t>
+          <t>경기 하남시 신장동로 130 4층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seline_pt</t>
+          <t>https://www.instagram.com/balanceon7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1671,7 +1667,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45s2o</t>
+          <t>https://talk.naver.com/ct/wp15ci4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1695,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>90</v>
+        <v>223</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>467</v>
       </c>
       <c r="R13" t="n">
-        <v>142</v>
+        <v>690</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1710,12 +1706,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1559021358</t>
+          <t>1660993198</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559021358</t>
+          <t>https://m.place.naver.com/place/1660993198</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3375</v>
+        <v>3378</v>
       </c>
       <c r="Q4" t="n">
         <v>666</v>
       </c>
       <c r="R4" t="n">
-        <v>4041</v>
+        <v>4044</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="Q5" t="n">
         <v>1341</v>
       </c>
       <c r="R5" t="n">
-        <v>2850</v>
+        <v>2856</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="Q6" t="n">
         <v>177</v>
       </c>
       <c r="R6" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1050,30 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에이원짐</t>
+          <t>카인드짐24시 헬스 PT 미사역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>aonegym8888@naver.com</t>
+          <t>kindgym8@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1459-2444</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
+          <t>경기 하남시 미사강변남로 125 미사역 마이움푸르지오시티 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aonegym8888</t>
+          <t>https://pf.kakao.com/_zxeEXK</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1083,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4czar</t>
+          <t>https://talk.naver.com/ct/w4m5k0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>103</v>
+        <v>1156</v>
       </c>
       <c r="Q7" t="n">
-        <v>730</v>
+        <v>1328</v>
       </c>
       <c r="R7" t="n">
-        <v>833</v>
+        <v>2484</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1771351174</t>
+          <t>1845162608</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771351174</t>
+          <t>https://m.place.naver.com/place/1845162608</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1148,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>온도짐 하남시청역점</t>
+          <t>에이원짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ondogym01@naver.com</t>
+          <t>aonegym8888@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>031-796-5025</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 하남대로 809 2층 온도짐</t>
+          <t>경기 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ondogym01</t>
+          <t>https://blog.naver.com/aonegym8888</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9c9c36</t>
+          <t>https://talk.naver.com/ct/w4czar</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>235</v>
+        <v>103</v>
       </c>
       <c r="Q8" t="n">
-        <v>84</v>
+        <v>729</v>
       </c>
       <c r="R8" t="n">
-        <v>319</v>
+        <v>832</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2009192948</t>
+          <t>1771351174</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2009192948</t>
+          <t>https://m.place.naver.com/place/1771351174</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="Q10" t="n">
         <v>2016</v>
       </c>
       <c r="R10" t="n">
-        <v>2927</v>
+        <v>2930</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q11" t="n">
         <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1532,29 +1532,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>셀린1:1PT스튜디오 북위례 본점</t>
+          <t>한걸음 트레이닝센터 하남 미사점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>seline_pt@naver.com</t>
+          <t>jw30-lim@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1464-2557</t>
+          <t>0507-1345-9570</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 하남시 위례학암로 23 1층</t>
+          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seline_pt</t>
+          <t>https://blog.naver.com/jw30-lim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45s2o</t>
+          <t>https://talk.naver.com/ct/w4au0e</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="R12" t="n">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,115 +1608,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1559021358</t>
+          <t>1350773756</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1559021358</t>
+          <t>https://m.place.naver.com/place/1350773756</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>하남 발란스온 필라테스</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>balanceon7@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1340-0381</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기 하남시 신장동로 130 4층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/balanceon7</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wp15ci4</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>223</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>467</v>
-      </c>
-      <c r="R13" t="n">
-        <v>690</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1660993198</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1660993198</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/하남_헬스장.xlsx
+++ b/naver-place-crawler/results_health/하남_헬스장.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -628,10 +628,10 @@
         <v>368</v>
       </c>
       <c r="Q2" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="R2" t="n">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>1515</v>
       </c>
       <c r="Q5" t="n">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="R5" t="n">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1050,34 +1050,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>카인드짐24시 헬스 PT 미사역점</t>
+          <t>에이원짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kindgym8@naver.com</t>
+          <t>aonegym8888@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1459-2444</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변남로 125 미사역 마이움푸르지오시티 B1</t>
+          <t>경기 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_zxeEXK</t>
+          <t>https://blog.naver.com/aonegym8888</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4m5k0</t>
+          <t>https://talk.naver.com/ct/w4czar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1156</v>
+        <v>103</v>
       </c>
       <c r="Q7" t="n">
-        <v>1328</v>
+        <v>729</v>
       </c>
       <c r="R7" t="n">
-        <v>2484</v>
+        <v>832</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1845162608</t>
+          <t>1771351174</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1845162608</t>
+          <t>https://m.place.naver.com/place/1771351174</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,30 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에이원짐</t>
+          <t>위드짐PT 하남미사</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>aonegym8888@naver.com</t>
+          <t>withgym01@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>031-8028-1929</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 295 2층 205~209호(망월동, 하남미 사 롯데캐슬 헤븐시티 II)</t>
+          <t>경기 하남시 미사강변대로 84 305, 306호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aonegym8888</t>
+          <t>https://blog.naver.com/withgym01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1186,14 +1186,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4czar</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="Q8" t="n">
-        <v>729</v>
+        <v>334</v>
       </c>
       <c r="R8" t="n">
-        <v>832</v>
+        <v>447</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1771351174</t>
+          <t>1010268294</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771351174</t>
+          <t>https://m.place.naver.com/place/1010268294</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>위드짐PT 하남미사</t>
+          <t>샤인휘트니스 미사역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>withgym01@naver.com</t>
+          <t>shine_fitness4@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-8028-1929</t>
+          <t>0507-1429-6523</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변대로 84 305, 306호</t>
+          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/withgym01</t>
+          <t>https://blog.naver.com/shine_fitness4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,10 +1280,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1sjoqj</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>113</v>
+        <v>914</v>
       </c>
       <c r="Q9" t="n">
-        <v>334</v>
+        <v>2016</v>
       </c>
       <c r="R9" t="n">
-        <v>447</v>
+        <v>2930</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1010268294</t>
+          <t>1377711586</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010268294</t>
+          <t>https://m.place.naver.com/place/1377711586</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1336,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>샤인휘트니스 미사역점</t>
+          <t>에어바이트 PT 미사점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shine_fitness4@naver.com</t>
+          <t>airbite@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1429-6523</t>
+          <t>0507-1332-4181</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 190 롯데캐슬스타 지하1층 (구)롯데스타휘트니스</t>
+          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shine_fitness4</t>
+          <t>https://www.instagram.com/_ko_coach</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1sjoqj</t>
+          <t>https://talk.naver.com/ct/wog61xv</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>914</v>
+        <v>93</v>
       </c>
       <c r="Q10" t="n">
-        <v>2016</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>2930</v>
+        <v>105</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1377711586</t>
+          <t>2000579553</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1377711586</t>
+          <t>https://m.place.naver.com/place/2000579553</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,29 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에어바이트 PT 미사점</t>
+          <t>한걸음 트레이닝센터 하남 미사점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>airbite@naver.com</t>
+          <t>jw30-lim@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1332-4181</t>
+          <t>0507-1345-9570</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변한강로 279 3층 311, 312호</t>
+          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ko_coach</t>
+          <t>https://blog.naver.com/jw30-lim</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wog61xv</t>
+          <t>https://talk.naver.com/ct/w4au0e</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="R11" t="n">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2000579553</t>
+          <t>1350773756</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2000579553</t>
+          <t>https://m.place.naver.com/place/1350773756</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1527,34 +1527,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한걸음 트레이닝센터 하남 미사점</t>
+          <t>하남 발란스온 필라테스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jw30-lim@naver.com</t>
+          <t>balanceon7@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1345-9570</t>
+          <t>0507-1340-0381</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 하남시 미사강변중앙로 165 신성프라자2 2층</t>
+          <t>경기 하남시 신장동로 130 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jw30-lim</t>
+          <t>https://www.instagram.com/balanceon7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4au0e</t>
+          <t>https://talk.naver.com/ct/wp15ci4</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>85</v>
+        <v>223</v>
       </c>
       <c r="Q12" t="n">
-        <v>109</v>
+        <v>467</v>
       </c>
       <c r="R12" t="n">
-        <v>194</v>
+        <v>690</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1350773756</t>
+          <t>1660993198</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1350773756</t>
+          <t>https://m.place.naver.com/place/1660993198</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
